--- a/artfynd/A 8186-2026 artfynd.xlsx
+++ b/artfynd/A 8186-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1286,6 +1286,626 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133720051</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58641</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>504529</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6612381</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133719822</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58291</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103008</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Curruca curruca</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>504680</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6612356</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Satt i kanten av skogen, flyttade sedan ut i kraftledningsgatan.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133718953</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58332</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>504490</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6612437</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133718843</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58243</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>504521</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6612361</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133719114</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58444</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>504603</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6612479</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>

--- a/artfynd/A 8186-2026 artfynd.xlsx
+++ b/artfynd/A 8186-2026 artfynd.xlsx
@@ -1293,27 +1293,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133720051</v>
+        <v>133719822</v>
       </c>
       <c r="B7" t="n">
-        <v>58641</v>
+        <v>58291</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>103008</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504529</v>
+        <v>504680</v>
       </c>
       <c r="R7" t="n">
-        <v>6612381</v>
+        <v>6612356</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1386,6 +1386,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Satt i kanten av skogen, flyttade sedan ut i kraftledningsgatan.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1416,27 +1421,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133719822</v>
+        <v>133720051</v>
       </c>
       <c r="B8" t="n">
-        <v>58291</v>
+        <v>58641</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103008</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1453,7 +1458,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1463,10 +1468,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504680</v>
+        <v>504529</v>
       </c>
       <c r="R8" t="n">
-        <v>6612356</v>
+        <v>6612381</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1509,11 +1514,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Satt i kanten av skogen, flyttade sedan ut i kraftledningsgatan.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1544,32 +1544,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133718953</v>
+        <v>133718843</v>
       </c>
       <c r="B9" t="n">
-        <v>58332</v>
+        <v>58243</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504490</v>
+        <v>504521</v>
       </c>
       <c r="R9" t="n">
-        <v>6612437</v>
+        <v>6612361</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1667,32 +1667,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133718843</v>
+        <v>133718953</v>
       </c>
       <c r="B10" t="n">
-        <v>58243</v>
+        <v>58332</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504521</v>
+        <v>504490</v>
       </c>
       <c r="R10" t="n">
-        <v>6612361</v>
+        <v>6612437</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>

--- a/artfynd/A 8186-2026 artfynd.xlsx
+++ b/artfynd/A 8186-2026 artfynd.xlsx
@@ -1293,27 +1293,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133719822</v>
+        <v>133720051</v>
       </c>
       <c r="B7" t="n">
-        <v>58291</v>
+        <v>58641</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103008</v>
+        <v>103044</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504680</v>
+        <v>504529</v>
       </c>
       <c r="R7" t="n">
-        <v>6612356</v>
+        <v>6612381</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1386,11 +1386,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Satt i kanten av skogen, flyttade sedan ut i kraftledningsgatan.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,27 +1416,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133720051</v>
+        <v>133719822</v>
       </c>
       <c r="B8" t="n">
-        <v>58641</v>
+        <v>58291</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>103008</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1458,7 +1453,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1468,10 +1463,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504529</v>
+        <v>504680</v>
       </c>
       <c r="R8" t="n">
-        <v>6612381</v>
+        <v>6612356</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1514,6 +1509,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Satt i kanten av skogen, flyttade sedan ut i kraftledningsgatan.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 8186-2026 artfynd.xlsx
+++ b/artfynd/A 8186-2026 artfynd.xlsx
@@ -1544,32 +1544,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133718843</v>
+        <v>133718953</v>
       </c>
       <c r="B9" t="n">
-        <v>58243</v>
+        <v>58332</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504521</v>
+        <v>504490</v>
       </c>
       <c r="R9" t="n">
-        <v>6612361</v>
+        <v>6612437</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1667,32 +1667,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133718953</v>
+        <v>133718843</v>
       </c>
       <c r="B10" t="n">
-        <v>58332</v>
+        <v>58243</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504490</v>
+        <v>504521</v>
       </c>
       <c r="R10" t="n">
-        <v>6612437</v>
+        <v>6612361</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>

--- a/artfynd/A 8186-2026 artfynd.xlsx
+++ b/artfynd/A 8186-2026 artfynd.xlsx
@@ -1544,32 +1544,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133718953</v>
+        <v>133718843</v>
       </c>
       <c r="B9" t="n">
-        <v>58332</v>
+        <v>58243</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504490</v>
+        <v>504521</v>
       </c>
       <c r="R9" t="n">
-        <v>6612437</v>
+        <v>6612361</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1667,32 +1667,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133718843</v>
+        <v>133718953</v>
       </c>
       <c r="B10" t="n">
-        <v>58243</v>
+        <v>58332</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504521</v>
+        <v>504490</v>
       </c>
       <c r="R10" t="n">
-        <v>6612361</v>
+        <v>6612437</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>

--- a/artfynd/A 8186-2026 artfynd.xlsx
+++ b/artfynd/A 8186-2026 artfynd.xlsx
@@ -1293,27 +1293,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133720051</v>
+        <v>133719822</v>
       </c>
       <c r="B7" t="n">
-        <v>58641</v>
+        <v>58291</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>103008</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504529</v>
+        <v>504680</v>
       </c>
       <c r="R7" t="n">
-        <v>6612381</v>
+        <v>6612356</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1386,6 +1386,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Satt i kanten av skogen, flyttade sedan ut i kraftledningsgatan.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1416,27 +1421,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133719822</v>
+        <v>133720051</v>
       </c>
       <c r="B8" t="n">
-        <v>58291</v>
+        <v>58641</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103008</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1453,7 +1458,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1463,10 +1468,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504680</v>
+        <v>504529</v>
       </c>
       <c r="R8" t="n">
-        <v>6612356</v>
+        <v>6612381</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1509,11 +1514,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Satt i kanten av skogen, flyttade sedan ut i kraftledningsgatan.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 8186-2026 artfynd.xlsx
+++ b/artfynd/A 8186-2026 artfynd.xlsx
@@ -1293,27 +1293,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133720051</v>
+        <v>133719822</v>
       </c>
       <c r="B7" t="n">
-        <v>58641</v>
+        <v>58291</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>103008</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504529</v>
+        <v>504680</v>
       </c>
       <c r="R7" t="n">
-        <v>6612381</v>
+        <v>6612356</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1386,6 +1386,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Satt i kanten av skogen, flyttade sedan ut i kraftledningsgatan.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1416,27 +1421,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133719822</v>
+        <v>133720051</v>
       </c>
       <c r="B8" t="n">
-        <v>58291</v>
+        <v>58641</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103008</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1453,7 +1458,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1463,10 +1468,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504680</v>
+        <v>504529</v>
       </c>
       <c r="R8" t="n">
-        <v>6612356</v>
+        <v>6612381</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1509,11 +1514,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Satt i kanten av skogen, flyttade sedan ut i kraftledningsgatan.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1544,32 +1544,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133718843</v>
+        <v>133718953</v>
       </c>
       <c r="B9" t="n">
-        <v>58243</v>
+        <v>58332</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504521</v>
+        <v>504490</v>
       </c>
       <c r="R9" t="n">
-        <v>6612361</v>
+        <v>6612437</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1667,32 +1667,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133718953</v>
+        <v>133718843</v>
       </c>
       <c r="B10" t="n">
-        <v>58332</v>
+        <v>58243</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504490</v>
+        <v>504521</v>
       </c>
       <c r="R10" t="n">
-        <v>6612437</v>
+        <v>6612361</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>

--- a/artfynd/A 8186-2026 artfynd.xlsx
+++ b/artfynd/A 8186-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1544,32 +1544,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133718953</v>
+        <v>133718843</v>
       </c>
       <c r="B9" t="n">
-        <v>58332</v>
+        <v>58243</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504490</v>
+        <v>504521</v>
       </c>
       <c r="R9" t="n">
-        <v>6612437</v>
+        <v>6612361</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1667,32 +1667,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133718843</v>
+        <v>133718953</v>
       </c>
       <c r="B10" t="n">
-        <v>58243</v>
+        <v>58332</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504521</v>
+        <v>504490</v>
       </c>
       <c r="R10" t="n">
-        <v>6612361</v>
+        <v>6612437</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1906,6 +1906,257 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134081934</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58332</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>504638</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6612451</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134081930</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58243</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>504638</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6612451</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Möjligen samma ex som utövade "revirstrid" ngt väster om denna koordinat.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>

--- a/artfynd/A 8186-2026 artfynd.xlsx
+++ b/artfynd/A 8186-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>133407823</v>
       </c>
       <c r="B3" t="n">
-        <v>58444</v>
+        <v>58451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>133408019</v>
       </c>
       <c r="B4" t="n">
-        <v>58332</v>
+        <v>58339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>133408003</v>
       </c>
       <c r="B5" t="n">
-        <v>58243</v>
+        <v>58250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>133408372</v>
       </c>
       <c r="B6" t="n">
-        <v>58444</v>
+        <v>58451</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>133719822</v>
       </c>
       <c r="B7" t="n">
-        <v>58291</v>
+        <v>58298</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>133720051</v>
       </c>
       <c r="B8" t="n">
-        <v>58641</v>
+        <v>58648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1544,32 +1544,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133718843</v>
+        <v>133718953</v>
       </c>
       <c r="B9" t="n">
-        <v>58243</v>
+        <v>58339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504521</v>
+        <v>504490</v>
       </c>
       <c r="R9" t="n">
-        <v>6612361</v>
+        <v>6612437</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1667,32 +1667,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133718953</v>
+        <v>133718843</v>
       </c>
       <c r="B10" t="n">
-        <v>58332</v>
+        <v>58250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504490</v>
+        <v>504521</v>
       </c>
       <c r="R10" t="n">
-        <v>6612437</v>
+        <v>6612361</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1793,7 +1793,7 @@
         <v>133719114</v>
       </c>
       <c r="B11" t="n">
-        <v>58444</v>
+        <v>58451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>134081934</v>
       </c>
       <c r="B12" t="n">
-        <v>58332</v>
+        <v>58339</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>134081930</v>
       </c>
       <c r="B13" t="n">
-        <v>58243</v>
+        <v>58250</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 8186-2026 artfynd.xlsx
+++ b/artfynd/A 8186-2026 artfynd.xlsx
@@ -1293,27 +1293,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133719822</v>
+        <v>133720051</v>
       </c>
       <c r="B7" t="n">
-        <v>58298</v>
+        <v>58648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103008</v>
+        <v>103044</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504680</v>
+        <v>504529</v>
       </c>
       <c r="R7" t="n">
-        <v>6612356</v>
+        <v>6612381</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1386,11 +1386,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Satt i kanten av skogen, flyttade sedan ut i kraftledningsgatan.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,27 +1416,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133720051</v>
+        <v>133719822</v>
       </c>
       <c r="B8" t="n">
-        <v>58648</v>
+        <v>58298</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>103008</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1458,7 +1453,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1468,10 +1463,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504529</v>
+        <v>504680</v>
       </c>
       <c r="R8" t="n">
-        <v>6612381</v>
+        <v>6612356</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1514,6 +1509,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Satt i kanten av skogen, flyttade sedan ut i kraftledningsgatan.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 8186-2026 artfynd.xlsx
+++ b/artfynd/A 8186-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>133407823</v>
       </c>
       <c r="B3" t="n">
-        <v>58451</v>
+        <v>58461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>133408019</v>
       </c>
       <c r="B4" t="n">
-        <v>58339</v>
+        <v>58349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>133408003</v>
       </c>
       <c r="B5" t="n">
-        <v>58250</v>
+        <v>58260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>133408372</v>
       </c>
       <c r="B6" t="n">
-        <v>58451</v>
+        <v>58461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,27 +1293,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133720051</v>
+        <v>133719822</v>
       </c>
       <c r="B7" t="n">
-        <v>58648</v>
+        <v>58308</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>103008</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504529</v>
+        <v>504680</v>
       </c>
       <c r="R7" t="n">
-        <v>6612381</v>
+        <v>6612356</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1386,6 +1386,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Satt i kanten av skogen, flyttade sedan ut i kraftledningsgatan.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1416,27 +1421,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133719822</v>
+        <v>133720051</v>
       </c>
       <c r="B8" t="n">
-        <v>58298</v>
+        <v>58658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103008</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1453,7 +1458,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1463,10 +1468,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504680</v>
+        <v>504529</v>
       </c>
       <c r="R8" t="n">
-        <v>6612356</v>
+        <v>6612381</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1509,11 +1514,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Satt i kanten av skogen, flyttade sedan ut i kraftledningsgatan.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1544,32 +1544,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133718953</v>
+        <v>133718843</v>
       </c>
       <c r="B9" t="n">
-        <v>58339</v>
+        <v>58260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504490</v>
+        <v>504521</v>
       </c>
       <c r="R9" t="n">
-        <v>6612437</v>
+        <v>6612361</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1667,32 +1667,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133718843</v>
+        <v>133718953</v>
       </c>
       <c r="B10" t="n">
-        <v>58250</v>
+        <v>58349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504521</v>
+        <v>504490</v>
       </c>
       <c r="R10" t="n">
-        <v>6612361</v>
+        <v>6612437</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1793,7 +1793,7 @@
         <v>133719114</v>
       </c>
       <c r="B11" t="n">
-        <v>58451</v>
+        <v>58461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>134081934</v>
       </c>
       <c r="B12" t="n">
-        <v>58339</v>
+        <v>58349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>134081930</v>
       </c>
       <c r="B13" t="n">
-        <v>58250</v>
+        <v>58260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 8186-2026 artfynd.xlsx
+++ b/artfynd/A 8186-2026 artfynd.xlsx
@@ -1293,27 +1293,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133719822</v>
+        <v>133720051</v>
       </c>
       <c r="B7" t="n">
-        <v>58308</v>
+        <v>58658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103008</v>
+        <v>103044</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504680</v>
+        <v>504529</v>
       </c>
       <c r="R7" t="n">
-        <v>6612356</v>
+        <v>6612381</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1386,11 +1386,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Satt i kanten av skogen, flyttade sedan ut i kraftledningsgatan.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,27 +1416,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133720051</v>
+        <v>133719822</v>
       </c>
       <c r="B8" t="n">
-        <v>58658</v>
+        <v>58308</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>103008</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1458,7 +1453,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1468,10 +1463,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504529</v>
+        <v>504680</v>
       </c>
       <c r="R8" t="n">
-        <v>6612381</v>
+        <v>6612356</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1514,6 +1509,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Satt i kanten av skogen, flyttade sedan ut i kraftledningsgatan.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 8186-2026 artfynd.xlsx
+++ b/artfynd/A 8186-2026 artfynd.xlsx
@@ -1293,27 +1293,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133720051</v>
+        <v>133719822</v>
       </c>
       <c r="B7" t="n">
-        <v>58658</v>
+        <v>58308</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>103008</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504529</v>
+        <v>504680</v>
       </c>
       <c r="R7" t="n">
-        <v>6612381</v>
+        <v>6612356</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1386,6 +1386,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Satt i kanten av skogen, flyttade sedan ut i kraftledningsgatan.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1416,27 +1421,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133719822</v>
+        <v>133720051</v>
       </c>
       <c r="B8" t="n">
-        <v>58308</v>
+        <v>58658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103008</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1453,7 +1458,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1463,10 +1468,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504680</v>
+        <v>504529</v>
       </c>
       <c r="R8" t="n">
-        <v>6612356</v>
+        <v>6612381</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1509,11 +1514,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Satt i kanten av skogen, flyttade sedan ut i kraftledningsgatan.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1544,32 +1544,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133718843</v>
+        <v>133718953</v>
       </c>
       <c r="B9" t="n">
-        <v>58260</v>
+        <v>58349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504521</v>
+        <v>504490</v>
       </c>
       <c r="R9" t="n">
-        <v>6612361</v>
+        <v>6612437</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1667,32 +1667,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133718953</v>
+        <v>133718843</v>
       </c>
       <c r="B10" t="n">
-        <v>58349</v>
+        <v>58260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504490</v>
+        <v>504521</v>
       </c>
       <c r="R10" t="n">
-        <v>6612437</v>
+        <v>6612361</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>

--- a/artfynd/A 8186-2026 artfynd.xlsx
+++ b/artfynd/A 8186-2026 artfynd.xlsx
@@ -1293,27 +1293,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133720051</v>
+        <v>133719822</v>
       </c>
       <c r="B7" t="n">
-        <v>58658</v>
+        <v>58308</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>103008</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504529</v>
+        <v>504680</v>
       </c>
       <c r="R7" t="n">
-        <v>6612381</v>
+        <v>6612356</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1386,6 +1386,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Satt i kanten av skogen, flyttade sedan ut i kraftledningsgatan.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1416,27 +1421,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133719822</v>
+        <v>133720051</v>
       </c>
       <c r="B8" t="n">
-        <v>58308</v>
+        <v>58658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103008</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1453,7 +1458,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1463,10 +1468,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504680</v>
+        <v>504529</v>
       </c>
       <c r="R8" t="n">
-        <v>6612356</v>
+        <v>6612381</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1509,11 +1514,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Satt i kanten av skogen, flyttade sedan ut i kraftledningsgatan.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 8186-2026 artfynd.xlsx
+++ b/artfynd/A 8186-2026 artfynd.xlsx
@@ -1544,32 +1544,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133718953</v>
+        <v>133718843</v>
       </c>
       <c r="B9" t="n">
-        <v>58349</v>
+        <v>58260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504490</v>
+        <v>504521</v>
       </c>
       <c r="R9" t="n">
-        <v>6612437</v>
+        <v>6612361</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1667,32 +1667,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133718843</v>
+        <v>133718953</v>
       </c>
       <c r="B10" t="n">
-        <v>58260</v>
+        <v>58349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504521</v>
+        <v>504490</v>
       </c>
       <c r="R10" t="n">
-        <v>6612361</v>
+        <v>6612437</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>

--- a/artfynd/A 8186-2026 artfynd.xlsx
+++ b/artfynd/A 8186-2026 artfynd.xlsx
@@ -1293,27 +1293,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133719822</v>
+        <v>133720051</v>
       </c>
       <c r="B7" t="n">
-        <v>58308</v>
+        <v>58658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103008</v>
+        <v>103044</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504680</v>
+        <v>504529</v>
       </c>
       <c r="R7" t="n">
-        <v>6612356</v>
+        <v>6612381</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1386,11 +1386,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Satt i kanten av skogen, flyttade sedan ut i kraftledningsgatan.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,27 +1416,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133720051</v>
+        <v>133719822</v>
       </c>
       <c r="B8" t="n">
-        <v>58658</v>
+        <v>58308</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>103008</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1458,7 +1453,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1468,10 +1463,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504529</v>
+        <v>504680</v>
       </c>
       <c r="R8" t="n">
-        <v>6612381</v>
+        <v>6612356</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1514,6 +1509,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Satt i kanten av skogen, flyttade sedan ut i kraftledningsgatan.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1544,32 +1544,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133718843</v>
+        <v>133718953</v>
       </c>
       <c r="B9" t="n">
-        <v>58260</v>
+        <v>58349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504521</v>
+        <v>504490</v>
       </c>
       <c r="R9" t="n">
-        <v>6612361</v>
+        <v>6612437</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1667,32 +1667,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133718953</v>
+        <v>133718843</v>
       </c>
       <c r="B10" t="n">
-        <v>58349</v>
+        <v>58260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504490</v>
+        <v>504521</v>
       </c>
       <c r="R10" t="n">
-        <v>6612437</v>
+        <v>6612361</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>

--- a/artfynd/A 8186-2026 artfynd.xlsx
+++ b/artfynd/A 8186-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>64639827</v>
+        <v>131874298</v>
       </c>
       <c r="B2" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4776</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100943</v>
+        <v>100299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>kolonier</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lejaområdet yta 7, Vstm</t>
+          <t>Gatan, Gatan, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504497.2173709042</v>
+        <v>504426</v>
       </c>
       <c r="R2" t="n">
-        <v>6612380.067793627</v>
+        <v>6612371</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,31 +740,26 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-07-30</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-09-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Räkning av larvkolonier inom Biogeografisk uppföljning av fjärilar.</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
@@ -785,26 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Claes Urban Eliasson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133407823</v>
+        <v>133407794</v>
       </c>
       <c r="B3" t="n">
-        <v>58461</v>
+        <v>58519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103018</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -848,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504636</v>
+        <v>504647</v>
       </c>
       <c r="R3" t="n">
-        <v>6612370</v>
+        <v>6612343</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -924,27 +905,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133408019</v>
+        <v>133719842</v>
       </c>
       <c r="B4" t="n">
-        <v>58349</v>
+        <v>58519</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -971,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504480</v>
+        <v>504654</v>
       </c>
       <c r="R4" t="n">
-        <v>6612365</v>
+        <v>6612328</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1001,22 +982,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,32 +1028,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133408003</v>
+        <v>133719822</v>
       </c>
       <c r="B5" t="n">
-        <v>58260</v>
+        <v>58308</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>103008</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1094,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504480</v>
+        <v>504680</v>
       </c>
       <c r="R5" t="n">
-        <v>6612365</v>
+        <v>6612356</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1124,22 +1105,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Satt i kanten av skogen, flyttade sedan ut i kraftledningsgatan.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133408372</v>
+        <v>133408003</v>
       </c>
       <c r="B6" t="n">
-        <v>58461</v>
+        <v>58260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,21 +1167,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103018</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1217,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504546</v>
+        <v>504480</v>
       </c>
       <c r="R6" t="n">
-        <v>6612358</v>
+        <v>6612365</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1293,32 +1279,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133720051</v>
+        <v>133718843</v>
       </c>
       <c r="B7" t="n">
-        <v>58658</v>
+        <v>58260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>103012</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1330,7 +1316,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1340,10 +1326,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504529</v>
+        <v>504521</v>
       </c>
       <c r="R7" t="n">
-        <v>6612381</v>
+        <v>6612361</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1416,10 +1402,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133719822</v>
+        <v>133718936</v>
       </c>
       <c r="B8" t="n">
-        <v>58308</v>
+        <v>58260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,21 +1413,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103008</v>
+        <v>103012</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1463,10 +1449,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504680</v>
+        <v>504445</v>
       </c>
       <c r="R8" t="n">
-        <v>6612356</v>
+        <v>6612403</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1509,11 +1495,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Satt i kanten av skogen, flyttade sedan ut i kraftledningsgatan.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1544,32 +1525,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133718953</v>
+        <v>134081763</v>
       </c>
       <c r="B9" t="n">
-        <v>58349</v>
+        <v>58260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1591,10 +1572,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504490</v>
+        <v>504520</v>
       </c>
       <c r="R9" t="n">
-        <v>6612437</v>
+        <v>6612358</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1621,7 +1602,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1631,12 +1612,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1667,7 +1648,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133718843</v>
+        <v>134081930</v>
       </c>
       <c r="B10" t="n">
         <v>58260</v>
@@ -1714,10 +1695,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504521</v>
+        <v>504638</v>
       </c>
       <c r="R10" t="n">
-        <v>6612361</v>
+        <v>6612451</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1744,7 +1725,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1754,12 +1735,17 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Möjligen samma ex som utövade "revirstrid" ngt väster om denna koordinat.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1790,10 +1776,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133719114</v>
+        <v>134381495</v>
       </c>
       <c r="B11" t="n">
-        <v>58461</v>
+        <v>58260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,21 +1787,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103018</v>
+        <v>103012</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1837,13 +1823,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>504603</v>
+        <v>504509</v>
       </c>
       <c r="R11" t="n">
-        <v>6612479</v>
+        <v>6612354</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1867,22 +1853,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1913,7 +1899,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134081934</v>
+        <v>133408019</v>
       </c>
       <c r="B12" t="n">
         <v>58349</v>
@@ -1960,10 +1946,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>504638</v>
+        <v>504480</v>
       </c>
       <c r="R12" t="n">
-        <v>6612451</v>
+        <v>6612365</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1990,22 +1976,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2036,32 +2022,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134081930</v>
+        <v>133718953</v>
       </c>
       <c r="B13" t="n">
-        <v>58260</v>
+        <v>58349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2083,10 +2069,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504638</v>
+        <v>504490</v>
       </c>
       <c r="R13" t="n">
-        <v>6612451</v>
+        <v>6612437</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2113,7 +2099,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2123,17 +2109,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Möjligen samma ex som utövade "revirstrid" ngt väster om denna koordinat.</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2157,6 +2138,1474 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134081771</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>504445</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6612366</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134081934</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>504638</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6612451</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133407823</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>504636</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6612370</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133408372</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>504546</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6612358</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133718774</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>504590</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6612336</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133719114</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>504603</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6612479</v>
+      </c>
+      <c r="S19" t="n">
+        <v>50</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134082081</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>504566</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6612344</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>133720051</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>504529</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6612381</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>133719024</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>504532</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6612459</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Spridd i området.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>133719011</v>
+      </c>
+      <c r="B23" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>504532</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6612459</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På flera platser i området.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>133719069</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101305</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>504532</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6612459</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Spridd i området.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>133719030</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>504532</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6612459</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spridd i området.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>

--- a/artfynd/A 8186-2026 artfynd.xlsx
+++ b/artfynd/A 8186-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131874298</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133407794</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133719842</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1153,6 +1173,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133719822</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1276,6 +1301,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133408003</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1399,6 +1429,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133718843</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1522,6 +1557,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133718936</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1645,6 +1685,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134081763</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1773,6 +1818,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134081930</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1896,6 +1946,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134381495</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2019,6 +2074,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133408019</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2142,6 +2202,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133718953</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2265,6 +2330,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134081771</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2388,6 +2458,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134081934</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2511,6 +2586,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133407823</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2634,6 +2714,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133408372</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2757,6 +2842,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133718774</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2880,6 +2970,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133719114</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3003,6 +3098,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134082081</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3124,6 +3224,11 @@
       <c r="AY21" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133720051</t>
         </is>
       </c>
     </row>
@@ -3247,6 +3352,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133719024</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3368,6 +3478,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133719011</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3489,6 +3604,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133719069</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3610,8 +3730,39 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133719030</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>